--- a/docs/MIS_March_2025_updated.xlsx
+++ b/docs/MIS_March_2025_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Desktop/developer/mis/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D89647-2BE3-E642-87DB-12E494B0EBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C3BC1A-6208-BD48-9F5F-35D9BCB4234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6171,7 +6171,7 @@
     <t>Turnover(Cr.)</t>
   </si>
   <si>
-    <t>AMRITA KIYER</t>
+    <t>MANOJ</t>
   </si>
 </sst>
 </file>
@@ -78150,11 +78150,11 @@
         <v>29500000</v>
       </c>
       <c r="K77" s="128">
-        <v>3430769</v>
+        <v>3045000</v>
       </c>
       <c r="L77" s="91">
         <f>J77-K77</f>
-        <v>26069231</v>
+        <v>26455000</v>
       </c>
       <c r="M77" s="19"/>
     </row>
